--- a/data/trans_orig/P16A20_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A20_2023-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2007</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393943</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395843</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>683730</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>685605</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585834</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>587849</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350314</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>938169</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940193</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>460889</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462909</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>375696</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>377699</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>838593</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>840608</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>310774</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312845</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>223365</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>534170</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>536209</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102950</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104810</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100692</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>203597</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>205502</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59238</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31829</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33561</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92823</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>94655</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42629</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44612</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1945671</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1947662</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1397753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1399722</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3345402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3347384</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2012</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326197</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>328123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>219167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>221087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>547282</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>549210</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>459003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>460974</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251531</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253542</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>712528</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714516</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>425269</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>427255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276245</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>703538</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>705554</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>320518</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322676</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186857</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189082</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>509570</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>511758</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103944</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73900</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33470</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28395</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61793</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1694758</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1696771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1056573</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1058637</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2753375</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2755408</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2016</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>324018</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>326043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>548790</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>550752</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>396417</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>398393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>294306</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296158</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692627</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>694551</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>422229</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>424225</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318149</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>742308</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>744258</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>310554</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>250848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>252896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>563475</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>565563</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164124</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166279</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99329</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101540</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>265631</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51791</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53730</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85073</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21458</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1702330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1704362</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1243977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1245925</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2948290</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2950287</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2023</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>22797</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23408</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32964</t>
+          <t>36925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378208</t>
+          <t>377190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289792</t>
+          <t>289528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308866</t>
+          <t>309023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680223</t>
+          <t>676262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706464</t>
+          <t>705113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24225</t>
+          <t>25179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416237</t>
+          <t>416267</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487279</t>
+          <t>486325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504091</t>
+          <t>503798</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908948</t>
+          <t>908851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926078</t>
+          <t>925944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25966</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43219</t>
+          <t>44652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29045</t>
+          <t>28838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48168</t>
+          <t>50287</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525187</t>
+          <t>525452</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535259</t>
+          <t>535107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>499249</t>
+          <t>497816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516502</t>
+          <t>516530</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1030638</t>
+          <t>1028519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1049761</t>
+          <t>1049968</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48953</t>
+          <t>50091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82632</t>
+          <t>81310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44507</t>
+          <t>42574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98091</t>
+          <t>97922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>867018</t>
+          <t>867246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>884200</t>
+          <t>884511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630249</t>
+          <t>631571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>663928</t>
+          <t>662790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1502576</t>
+          <t>1502745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1556160</t>
+          <t>1558093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59839</t>
+          <t>59084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82919</t>
+          <t>83946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66324</t>
+          <t>65956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93014</t>
+          <t>94021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>545825</t>
+          <t>545901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>556234</t>
+          <t>556439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>461321</t>
+          <t>460294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>484401</t>
+          <t>485156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1011463</t>
+          <t>1010456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1038153</t>
+          <t>1038521</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68273</t>
+          <t>67686</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>458550</t>
+          <t>468388</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67692</t>
+          <t>67671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>633501</t>
+          <t>591473</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>60,59%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>353280</t>
+          <t>353508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363683</t>
+          <t>363178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149460</t>
+          <t>139622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>539737</t>
+          <t>540324</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>342675</t>
+          <t>384703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>908484</t>
+          <t>908505</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33170</t>
+          <t>33390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50975</t>
+          <t>51110</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>37771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56881</t>
+          <t>59398</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271064</t>
+          <t>271289</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>279726</t>
+          <t>279631</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>373750</t>
+          <t>373615</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>391555</t>
+          <t>391335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>650603</t>
+          <t>648086</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>669963</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30900</t>
+          <t>31327</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62529</t>
+          <t>61801</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>288444</t>
+          <t>287815</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1032918</t>
+          <t>1179965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>323603</t>
+          <t>322547</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1233134</t>
+          <t>1247335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3396291</t>
+          <t>3397019</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3427920</t>
+          <t>3427493</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2624110</t>
+          <t>2477063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3368584</t>
+          <t>3369213</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5882714</t>
+          <t>5868513</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6792245</t>
+          <t>6793301</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A20_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A20_2023-Edad-trans_orig.xlsx
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22797</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23672</t>
+          <t>27993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36925</t>
+          <t>35687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>394338</t>
+          <t>402667</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377190</t>
+          <t>383741</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>302385</t>
+          <t>349292</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289528</t>
+          <t>334519</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309023</t>
+          <t>356301</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>696723</t>
+          <t>751959</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676262</t>
+          <t>734618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>705113</t>
+          <t>761908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25179</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>18993</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26200</t>
+          <t>28893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>422186</t>
+          <t>475530</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416267</t>
+          <t>469948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>496624</t>
+          <t>483450</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486325</t>
+          <t>472956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503798</t>
+          <t>490464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>918809</t>
+          <t>958980</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908851</t>
+          <t>949080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925944</t>
+          <t>967017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>37273</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25938</t>
+          <t>28055</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44652</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37561</t>
+          <t>41525</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28838</t>
+          <t>31752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50287</t>
+          <t>52977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>532037</t>
+          <t>616585</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525452</t>
+          <t>610719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535107</t>
+          <t>619723</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>509208</t>
+          <t>584866</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>497816</t>
+          <t>573766</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516530</t>
+          <t>594084</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1041245</t>
+          <t>1201451</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1028519</t>
+          <t>1189999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1049968</t>
+          <t>1211224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20540</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62628</t>
+          <t>62303</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50091</t>
+          <t>51939</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81310</t>
+          <t>75024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>73543</t>
+          <t>73048</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42574</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97922</t>
+          <t>88702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>876871</t>
+          <t>689872</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>867246</t>
+          <t>682059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>884511</t>
+          <t>695500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>650253</t>
+          <t>674583</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>631571</t>
+          <t>661862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>662790</t>
+          <t>684947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1527124</t>
+          <t>1364456</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1502745</t>
+          <t>1348802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1558093</t>
+          <t>1377084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>70705</t>
+          <t>80871</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59084</t>
+          <t>69462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83946</t>
+          <t>96701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>78957</t>
+          <t>90615</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65956</t>
+          <t>76692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94021</t>
+          <t>106587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>551986</t>
+          <t>598615</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>545901</t>
+          <t>591695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>556439</t>
+          <t>603312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>473535</t>
+          <t>525853</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460294</t>
+          <t>510023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>485156</t>
+          <t>537262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1025520</t>
+          <t>1124468</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1010456</t>
+          <t>1108496</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1038521</t>
+          <t>1138391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544240</t>
+          <t>606724</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544240</t>
+          <t>606724</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544240</t>
+          <t>606724</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104477</t>
+          <t>1215083</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104477</t>
+          <t>1215083</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104477</t>
+          <t>1215083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>252918</t>
+          <t>54470</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67686</t>
+          <t>44894</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>468388</t>
+          <t>65747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>261556</t>
+          <t>63832</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67671</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>591473</t>
+          <t>76095</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>359527</t>
+          <t>397718</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>353508</t>
+          <t>391409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363178</t>
+          <t>402222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>355092</t>
+          <t>384317</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>139622</t>
+          <t>373040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>540324</t>
+          <t>393893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>714620</t>
+          <t>782035</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>384703</t>
+          <t>769772</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>908505</t>
+          <t>792687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608010</t>
+          <t>438787</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608010</t>
+          <t>438787</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608010</t>
+          <t>438787</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976176</t>
+          <t>845867</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976176</t>
+          <t>845867</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976176</t>
+          <t>845867</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41047</t>
+          <t>45288</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33390</t>
+          <t>36625</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51110</t>
+          <t>55816</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>47054</t>
+          <t>52104</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37771</t>
+          <t>42983</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59398</t>
+          <t>65532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>276752</t>
+          <t>303382</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271289</t>
+          <t>298021</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>279631</t>
+          <t>306845</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>383678</t>
+          <t>418122</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>373615</t>
+          <t>407594</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>391335</t>
+          <t>426785</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>660430</t>
+          <t>721504</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>648086</t>
+          <t>708076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>730625</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>47404</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31327</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61801</t>
+          <t>63640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>486253</t>
+          <t>311059</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>287815</t>
+          <t>283571</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1179965</t>
+          <t>344144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>531377</t>
+          <t>358463</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>322547</t>
+          <t>327281</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1247335</t>
+          <t>389166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3413696</t>
+          <t>3484371</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3397019</t>
+          <t>3468135</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3427493</t>
+          <t>3497563</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3170775</t>
+          <t>3420483</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2477063</t>
+          <t>3387398</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3369213</t>
+          <t>3447971</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6584471</t>
+          <t>6904853</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5868513</t>
+          <t>6874150</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6793301</t>
+          <t>6936035</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657028</t>
+          <t>3731542</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657028</t>
+          <t>3731542</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657028</t>
+          <t>3731542</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115848</t>
+          <t>7263316</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115848</t>
+          <t>7263316</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115848</t>
+          <t>7263316</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
